--- a/vse-loti/341340906/spec-341340906.xlsx
+++ b/vse-loti/341340906/spec-341340906.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -558,7 +561,7 @@
         <v>211082.79</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +596,7 @@
         <v>255538.52</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>306646.23</v>
+        <v>311757</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +631,7 @@
         <v>255538.52</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>306646.23</v>
+        <v>311757</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +666,7 @@
         <v>193984.43</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>232781.31</v>
+        <v>236661</v>
       </c>
     </row>
     <row r="6">
@@ -698,7 +701,7 @@
         <v>211082.79</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="7">
@@ -733,7 +736,7 @@
         <v>206808.2</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>248169.84</v>
+        <v>252306</v>
       </c>
     </row>
     <row r="8">
@@ -768,7 +771,7 @@
         <v>255538.52</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>306646.23</v>
+        <v>311757</v>
       </c>
     </row>
     <row r="9">
@@ -803,7 +806,7 @@
         <v>211082.79</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +841,7 @@
         <v>211082.79</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="11">
@@ -873,7 +876,7 @@
         <v>211082.79</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="12">
@@ -908,7 +911,7 @@
         <v>292300</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>350760</v>
+        <v>356606</v>
       </c>
     </row>
     <row r="13">
@@ -943,7 +946,7 @@
         <v>292300</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>350760</v>
+        <v>356606</v>
       </c>
     </row>
     <row r="14">
@@ -978,7 +981,7 @@
         <v>206808.2</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>248169.84</v>
+        <v>252306</v>
       </c>
     </row>
     <row r="15">
@@ -1013,7 +1016,7 @@
         <v>211082.79</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="16">
@@ -1048,7 +1051,7 @@
         <v>206808.2</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>248169.84</v>
+        <v>252306</v>
       </c>
     </row>
     <row r="17">
@@ -1083,7 +1086,7 @@
         <v>211082.79</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="18">
@@ -1118,7 +1121,7 @@
         <v>292300</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>350760</v>
+        <v>356606</v>
       </c>
     </row>
     <row r="19">
@@ -1153,7 +1156,7 @@
         <v>292300</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>350760</v>
+        <v>356606</v>
       </c>
     </row>
     <row r="20">
@@ -1188,7 +1191,7 @@
         <v>193984.43</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>232781.31</v>
+        <v>236661</v>
       </c>
     </row>
     <row r="21">
@@ -1223,7 +1226,7 @@
         <v>189709.84</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>227651.8</v>
+        <v>231446</v>
       </c>
     </row>
     <row r="22">
@@ -1258,7 +1261,7 @@
         <v>189709.84</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>227651.8</v>
+        <v>231446</v>
       </c>
     </row>
     <row r="23">
@@ -1293,7 +1296,7 @@
         <v>211082.79</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="24">
@@ -1328,7 +1331,7 @@
         <v>189709.84</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>227651.8</v>
+        <v>231446</v>
       </c>
     </row>
     <row r="25">
@@ -1363,7 +1366,7 @@
         <v>189709.84</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>227651.8</v>
+        <v>231446</v>
       </c>
     </row>
     <row r="26">
@@ -1398,7 +1401,7 @@
         <v>211082.79</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="27">
@@ -1433,7 +1436,7 @@
         <v>211082.79</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="28">
@@ -1468,7 +1471,7 @@
         <v>255538.52</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>306646.23</v>
+        <v>311757</v>
       </c>
     </row>
     <row r="29">
@@ -1503,7 +1506,7 @@
         <v>211082.79</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="30">
@@ -1538,7 +1541,7 @@
         <v>211082.79</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="31">
@@ -1573,7 +1576,7 @@
         <v>255538.52</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>306646.23</v>
+        <v>311757</v>
       </c>
     </row>
     <row r="32">
@@ -1608,7 +1611,7 @@
         <v>211082.79</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="33">
@@ -1643,7 +1646,7 @@
         <v>598360.66</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>718032.79</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="34">
@@ -1678,7 +1681,7 @@
         <v>598360.66</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>718032.79</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="35">
@@ -1713,7 +1716,7 @@
         <v>189709.84</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>227651.8</v>
+        <v>231446</v>
       </c>
     </row>
     <row r="36">
@@ -1748,7 +1751,7 @@
         <v>598360.66</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>718032.79</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="37">
@@ -1783,7 +1786,7 @@
         <v>292300</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>350760</v>
+        <v>356606</v>
       </c>
     </row>
     <row r="38">
@@ -1818,7 +1821,7 @@
         <v>478672.13</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>574406.5600000001</v>
+        <v>583980</v>
       </c>
     </row>
     <row r="39">
@@ -1853,7 +1856,7 @@
         <v>393180.34</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>471816.4</v>
+        <v>479680.01</v>
       </c>
     </row>
     <row r="40">
@@ -1888,7 +1891,7 @@
         <v>211082.79</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="41">
@@ -1923,7 +1926,7 @@
         <v>211082.79</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="42">
@@ -1958,7 +1961,7 @@
         <v>393180.34</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>471816.4</v>
+        <v>479680.01</v>
       </c>
     </row>
     <row r="43">
@@ -1993,7 +1996,7 @@
         <v>211082.79</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="44">
@@ -2028,7 +2031,7 @@
         <v>211082.79</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>253299.34</v>
+        <v>257521</v>
       </c>
     </row>
     <row r="45">
@@ -2063,7 +2066,7 @@
         <v>189344.26</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>227213.11</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="46">
@@ -2089,18 +2092,35 @@
         <v>3866229.98</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22%:</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>4716800.58</v>
+      </c>
+    </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
+          <t>НДС 22 %, ставка из документа: "с НДС 22%" — Приложение №4. Сведения о НМЦ ед. товара.txt; закупка по 223-ФЗ, включать налоги в цену закон не требует — суммы взяты как в документе («без НДС»). «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
           <t>Источник: Приложение №4. Сведения о НМЦ ед. товара.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A49:B51"/>
+    <mergeCell ref="A51:B53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341340906/spec-341340906.xlsx
+++ b/vse-loti/341340906/spec-341340906.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,17 +516,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -555,13 +561,16 @@
         <v>0.2</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>42216.56</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>51504.2</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +599,16 @@
         <v>0.15</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>255538.52</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>38330.78</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>255538.52</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>311757</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>46763.55</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +637,16 @@
         <v>0.1</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>255538.52</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>25553.85</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>255538.52</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>311757</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>31175.7</v>
       </c>
     </row>
     <row r="5">
@@ -660,13 +675,16 @@
         <v>0.2</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>193984.43</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>38796.89</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>193984.43</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>236661</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>47332.21</v>
       </c>
     </row>
     <row r="6">
@@ -695,13 +713,16 @@
         <v>0.15</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>31662.42</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>38628.15</v>
       </c>
     </row>
     <row r="7">
@@ -730,13 +751,16 @@
         <v>0.3</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>206808.2</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>62042.46</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>206808.2</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>252306</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>75691.8</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +789,16 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>255538.52</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>22487.39</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>255538.52</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>311757</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>27434.62</v>
       </c>
     </row>
     <row r="9">
@@ -800,13 +827,16 @@
         <v>0.5</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>105541.39</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>128760.5</v>
       </c>
     </row>
     <row r="10">
@@ -835,13 +865,16 @@
         <v>0.3</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>63324.84</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>77256.3</v>
       </c>
     </row>
     <row r="11">
@@ -870,13 +903,16 @@
         <v>0.1</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="12">
@@ -905,13 +941,16 @@
         <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>292300</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>14615</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>292300</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>356606</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>17830.3</v>
       </c>
     </row>
     <row r="13">
@@ -940,13 +979,16 @@
         <v>0.05</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>292300</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>14615</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>292300</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>356606</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>17830.3</v>
       </c>
     </row>
     <row r="14">
@@ -975,13 +1017,16 @@
         <v>0.1</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>206808.2</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>20680.82</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>206808.2</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>252306</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>25230.6</v>
       </c>
     </row>
     <row r="15">
@@ -1010,13 +1055,16 @@
         <v>0.1</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="16">
@@ -1045,13 +1093,16 @@
         <v>0.2</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>206808.2</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>41361.64</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>206808.2</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>252306</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>50461.2</v>
       </c>
     </row>
     <row r="17">
@@ -1080,13 +1131,16 @@
         <v>0.1</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="18">
@@ -1115,13 +1169,16 @@
         <v>0.05</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>292300</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>14615</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>292300</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>356606</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>17830.3</v>
       </c>
     </row>
     <row r="19">
@@ -1150,13 +1207,16 @@
         <v>0.05</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>292300</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>14615</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>292300</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>356606</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>17830.3</v>
       </c>
     </row>
     <row r="20">
@@ -1185,13 +1245,16 @@
         <v>0.1</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>193984.43</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>19398.44</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>193984.43</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>236661</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>23666.1</v>
       </c>
     </row>
     <row r="21">
@@ -1220,13 +1283,16 @@
         <v>0.15</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>189709.84</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>28456.48</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>189709.84</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>231446</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>34716.91</v>
       </c>
     </row>
     <row r="22">
@@ -1255,13 +1321,16 @@
         <v>0.15</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>189709.84</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>28456.48</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>189709.84</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>231446</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>34716.91</v>
       </c>
     </row>
     <row r="23">
@@ -1290,13 +1359,16 @@
         <v>0.08</v>
       </c>
       <c r="G23" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>16886.62</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>20601.68</v>
       </c>
     </row>
     <row r="24">
@@ -1325,13 +1397,16 @@
         <v>0.2</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>189709.84</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>37941.97</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>189709.84</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>231446</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>46289.2</v>
       </c>
     </row>
     <row r="25">
@@ -1360,13 +1435,16 @@
         <v>0.28</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>189709.84</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>53118.75</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>189709.84</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>231446</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>64804.88</v>
       </c>
     </row>
     <row r="26">
@@ -1395,13 +1473,16 @@
         <v>0.04</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>8443.309999999999</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>10300.84</v>
       </c>
     </row>
     <row r="27">
@@ -1430,13 +1511,16 @@
         <v>0.1</v>
       </c>
       <c r="G27" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="28">
@@ -1465,13 +1549,16 @@
         <v>0.1</v>
       </c>
       <c r="G28" s="5" t="n">
+        <v>255538.52</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>25553.85</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>255538.52</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>311757</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>31175.7</v>
       </c>
     </row>
     <row r="29">
@@ -1500,13 +1587,16 @@
         <v>0.1</v>
       </c>
       <c r="G29" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,13 +1625,16 @@
         <v>0.1</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="31">
@@ -1570,13 +1663,16 @@
         <v>0.1</v>
       </c>
       <c r="G31" s="5" t="n">
+        <v>255538.52</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>25553.85</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>255538.52</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>311757</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>31175.7</v>
       </c>
     </row>
     <row r="32">
@@ -1605,13 +1701,16 @@
         <v>0.1</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="33">
@@ -1640,13 +1739,16 @@
         <v>0.042</v>
       </c>
       <c r="G33" s="5" t="n">
+        <v>598360.66</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>25131.15</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>598360.66</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>730000</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>30660</v>
       </c>
     </row>
     <row r="34">
@@ -1675,13 +1777,16 @@
         <v>0.042</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>598360.66</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>25131.15</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>598360.66</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>730000</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>30660</v>
       </c>
     </row>
     <row r="35">
@@ -1710,13 +1815,16 @@
         <v>3</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>189709.84</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>569129.51</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>189709.84</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>231446</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>694338</v>
       </c>
     </row>
     <row r="36">
@@ -1745,13 +1853,16 @@
         <v>0.05</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>598360.66</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>29918.03</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>598360.66</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>730000</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>36500</v>
       </c>
     </row>
     <row r="37">
@@ -1780,13 +1891,16 @@
         <v>0.1</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>292300</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>29230</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>292300</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>356606</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>35660.6</v>
       </c>
     </row>
     <row r="38">
@@ -1815,13 +1929,16 @@
         <v>0.1</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>478672.13</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>47867.21</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>478672.13</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>583980</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>58398</v>
       </c>
     </row>
     <row r="39">
@@ -1850,13 +1967,16 @@
         <v>0.002</v>
       </c>
       <c r="G39" s="5" t="n">
+        <v>393180.34</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>786.36</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>393180.34</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>479680.01</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>959.36</v>
       </c>
     </row>
     <row r="40">
@@ -1885,13 +2005,16 @@
         <v>0.1</v>
       </c>
       <c r="G40" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="41">
@@ -1920,13 +2043,16 @@
         <v>0.1</v>
       </c>
       <c r="G41" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>21108.28</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>25752.1</v>
       </c>
     </row>
     <row r="42">
@@ -1955,13 +2081,16 @@
         <v>0.1</v>
       </c>
       <c r="G42" s="5" t="n">
+        <v>393180.34</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>39318.03</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>393180.34</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>479680.01</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>47968</v>
       </c>
     </row>
     <row r="43">
@@ -1990,13 +2119,16 @@
         <v>0.2</v>
       </c>
       <c r="G43" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>42216.56</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>51504.2</v>
       </c>
     </row>
     <row r="44">
@@ -2025,13 +2157,16 @@
         <v>0.24</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>211082.79</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>50659.87</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>211082.79</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>257521</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>61805.04</v>
       </c>
     </row>
     <row r="45">
@@ -2060,14 +2195,17 @@
         <v>7</v>
       </c>
       <c r="G45" s="5" t="n">
+        <v>189344.26</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>1325409.83</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>189344.26</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>231000</v>
       </c>
+      <c r="J45" s="5" t="n">
+        <v>1616999.99</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -2079,7 +2217,16 @@
         <v>15.464</v>
       </c>
       <c r="G46" s="9" t="n">
+        <v>204930.23</v>
+      </c>
+      <c r="H46" s="9" t="n">
         <v>3169041.01</v>
+      </c>
+      <c r="I46" s="9" t="n">
+        <v>250014.88</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>3866230.03</v>
       </c>
     </row>
     <row r="47">
@@ -2088,7 +2235,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="H47" s="9" t="n">
         <v>3866229.98</v>
       </c>
     </row>
@@ -2098,7 +2245,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="J48" s="9" t="n">
         <v>4716800.58</v>
       </c>
     </row>
